--- a/game54/web.xlsx
+++ b/game54/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21975" windowHeight="13665"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="13" r:id="rId1"/>
@@ -71,7 +71,7 @@
     <t>#6090b8</t>
   </si>
   <si>
-    <t>acatalepsy.site</t>
+    <t>ethergaunt.com</t>
   </si>
   <si>
     <t>#4d613c</t>
@@ -153,7 +153,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -227,6 +227,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF20A53A"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -753,148 +759,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -946,9 +952,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -960,6 +963,14 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment/>
+      <extLst>
+        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
+          <etc:displayText val="2"/>
+        </ext>
+      </extLst>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1376,10 +1387,10 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="3"/>
@@ -1392,10 +1403,10 @@
       <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="3"/>
@@ -1408,10 +1419,10 @@
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="19" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="12"/>
@@ -1424,10 +1435,10 @@
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="20" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="12"/>
@@ -1440,7 +1451,7 @@
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="22" t="s">

--- a/game54/web.xlsx
+++ b/game54/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="19620" windowHeight="11670"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="13" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
   <si>
     <t>domain</t>
   </si>
@@ -47,49 +47,61 @@
     <t>json</t>
   </si>
   <si>
-    <t>reticence.cloud</t>
+    <t>play.happwave.com</t>
+  </si>
+  <si>
+    <t>#dfbc1f</t>
+  </si>
+  <si>
+    <t>sec.happwave.com</t>
+  </si>
+  <si>
+    <t>#284fef</t>
+  </si>
+  <si>
+    <t>game.happwave.com</t>
+  </si>
+  <si>
+    <t>#ff5b00</t>
+  </si>
+  <si>
+    <t>play.cheiloproclitic.com</t>
+  </si>
+  <si>
+    <t>#f53d93</t>
+  </si>
+  <si>
+    <t>sec.cheiloproclitic.com</t>
+  </si>
+  <si>
+    <t>#ff978a</t>
+  </si>
+  <si>
+    <t>game.cheiloproclitic.com</t>
+  </si>
+  <si>
+    <t>#6ae966</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>hfwinfo.top</t>
   </si>
   <si>
     <t>#664b3a</t>
   </si>
   <si>
-    <t>whirpool.fun</t>
+    <t>jkif.top</t>
   </si>
   <si>
     <t>#e07563</t>
   </si>
   <si>
-    <t>happwave.com</t>
+    <t>mcif.top</t>
   </si>
   <si>
     <t>#41bbcb</t>
-  </si>
-  <si>
-    <t>cheiloproclitic.com</t>
-  </si>
-  <si>
-    <t>#6090b8</t>
-  </si>
-  <si>
-    <t>ethergaunt.com</t>
-  </si>
-  <si>
-    <t>#4d613c</t>
-  </si>
-  <si>
-    <t>color</t>
-  </si>
-  <si>
-    <t>adoxography.site</t>
-  </si>
-  <si>
-    <t>#e67762</t>
-  </si>
-  <si>
-    <t>anthypophora.com</t>
-  </si>
-  <si>
-    <t>#663d74</t>
   </si>
   <si>
     <t>haberdasher.cloud</t>
@@ -194,15 +206,10 @@
     <font>
       <u/>
       <sz val="10"/>
-      <color rgb="FF2972F4"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -215,10 +222,9 @@
     <font>
       <u/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF2972F4"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -229,10 +235,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF20A53A"/>
-      <name val="Arial"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFCE9178"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -378,7 +393,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="46">
+  <fills count="48">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -423,18 +438,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE67762"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF663D74"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF664B3A"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -453,13 +456,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6090B8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4D613C"/>
+        <fgColor rgb="FFDFBC1F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF284FEF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF5B00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF53D93"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF978A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AE966"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -650,12 +677,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -780,7 +822,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -792,119 +834,119 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -931,29 +973,38 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -964,15 +1015,16 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1387,10 +1439,10 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="3"/>
@@ -1398,15 +1450,15 @@
         <v>1</v>
       </c>
       <c r="E2" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="22" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="3"/>
@@ -1414,47 +1466,47 @@
         <v>2</v>
       </c>
       <c r="E3" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="12"/>
+      <c r="C4" s="16"/>
       <c r="D4" s="3">
         <v>3</v>
       </c>
       <c r="E4" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="12"/>
+      <c r="C5" s="25"/>
       <c r="D5" s="3">
         <v>4</v>
       </c>
       <c r="E5" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="26" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="12"/>
@@ -1462,16 +1514,24 @@
         <v>5</v>
       </c>
       <c r="E6" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
+      <c r="A7" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>16</v>
+      </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>13</v>
+      </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
@@ -1483,6 +1543,14 @@
       <c r="F8" s="3"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="play.happwave.com" tooltip="http://happwave.com"/>
+    <hyperlink ref="A3" r:id="rId1" display="sec.happwave.com" tooltip="http://happwave.com"/>
+    <hyperlink ref="A4" r:id="rId2" display="game.happwave.com" tooltip="http://game.happwave.com"/>
+    <hyperlink ref="A5" r:id="rId3" display="play.cheiloproclitic.com" tooltip="http://play.cheiloproclitic.com"/>
+    <hyperlink ref="A6" r:id="rId4" display="sec.cheiloproclitic.com" tooltip="http://sec.cheiloproclitic.com"/>
+    <hyperlink ref="A7" r:id="rId5" display="game.cheiloproclitic.com" tooltip="http://game.cheiloproclitic.com"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1502,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1510,188 +1578,195 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="14"/>
+      <c r="A4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="16"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="14"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F16" r:id="rId1"/>
     <hyperlink ref="F17" r:id="rId2"/>
+    <hyperlink ref="A2" r:id="rId3" display="hfwinfo.top" tooltip="http://hfwinfo.top"/>
+    <hyperlink ref="A3" r:id="rId4" display="jkif.top" tooltip="http://jkif.top"/>
+    <hyperlink ref="A4" r:id="rId5" display="mcif.top" tooltip="http://mcif.top"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1726,10 +1801,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1740,10 +1815,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1754,10 +1829,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1768,10 +1843,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1782,10 +1857,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1811,25 +1886,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7">

--- a/game54/web.xlsx
+++ b/game54/web.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>domain</t>
   </si>
@@ -47,40 +47,28 @@
     <t>json</t>
   </si>
   <si>
-    <t>play.happwave.com</t>
-  </si>
-  <si>
-    <t>#dfbc1f</t>
-  </si>
-  <si>
-    <t>sec.happwave.com</t>
-  </si>
-  <si>
-    <t>#284fef</t>
-  </si>
-  <si>
-    <t>game.happwave.com</t>
-  </si>
-  <si>
-    <t>#ff5b00</t>
-  </si>
-  <si>
-    <t>play.cheiloproclitic.com</t>
-  </si>
-  <si>
-    <t>#f53d93</t>
-  </si>
-  <si>
-    <t>sec.cheiloproclitic.com</t>
-  </si>
-  <si>
-    <t>#ff978a</t>
-  </si>
-  <si>
-    <t>game.cheiloproclitic.com</t>
-  </si>
-  <si>
-    <t>#6ae966</t>
+    <t>veridict.fun</t>
+  </si>
+  <si>
+    <t>#a515f9</t>
+  </si>
+  <si>
+    <t>xeromancer.cloud</t>
+  </si>
+  <si>
+    <t>#00000e</t>
+  </si>
+  <si>
+    <t>balefire.cloud</t>
+  </si>
+  <si>
+    <t>#73AE52</t>
+  </si>
+  <si>
+    <t>puttable.site</t>
+  </si>
+  <si>
+    <t>#ffb400</t>
   </si>
   <si>
     <t>color</t>
@@ -165,7 +153,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -235,6 +223,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color rgb="FFCE9178"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFBF1D7"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -243,13 +245,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FFCE9178"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -393,7 +388,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="48">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -456,37 +451,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDFBC1F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF284FEF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF5B00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF53D93"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF978A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AE966"/>
+        <fgColor rgb="FFA515F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00000E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73AE52"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFB400"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -801,79 +784,85 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -882,10 +871,10 @@
     <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -894,10 +883,10 @@
     <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -906,10 +895,10 @@
     <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -918,10 +907,10 @@
     <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -930,23 +919,17 @@
     <xf numFmtId="0" fontId="29" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1003,29 +986,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1447,10 +1427,10 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3"/>
     </row>
@@ -1463,10 +1443,10 @@
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3"/>
     </row>
@@ -1479,10 +1459,10 @@
       </c>
       <c r="C4" s="16"/>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="3"/>
     </row>
@@ -1495,43 +1475,27 @@
       </c>
       <c r="C5" s="25"/>
       <c r="D5" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="3">
-        <v>5</v>
-      </c>
-      <c r="E6" s="3">
-        <v>12</v>
-      </c>
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>13</v>
-      </c>
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
@@ -1544,12 +1508,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="play.happwave.com" tooltip="http://happwave.com"/>
-    <hyperlink ref="A3" r:id="rId1" display="sec.happwave.com" tooltip="http://happwave.com"/>
-    <hyperlink ref="A4" r:id="rId2" display="game.happwave.com" tooltip="http://game.happwave.com"/>
-    <hyperlink ref="A5" r:id="rId3" display="play.cheiloproclitic.com" tooltip="http://play.cheiloproclitic.com"/>
-    <hyperlink ref="A6" r:id="rId4" display="sec.cheiloproclitic.com" tooltip="http://sec.cheiloproclitic.com"/>
-    <hyperlink ref="A7" r:id="rId5" display="game.cheiloproclitic.com" tooltip="http://game.cheiloproclitic.com"/>
+    <hyperlink ref="A7" r:id="rId1" tooltip="http://game.cheiloproclitic.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1570,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1578,28 +1537,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="16"/>
@@ -1801,10 +1760,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1815,10 +1774,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1829,10 +1788,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1843,10 +1802,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1857,10 +1816,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1886,25 +1845,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7">

--- a/game54/web.xlsx
+++ b/game54/web.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19620" windowHeight="11670"/>
+    <workbookView windowWidth="14475" windowHeight="10890"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="13" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="15" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="14" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="15" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="13" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="16" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>domain</t>
   </si>
@@ -47,79 +47,70 @@
     <t>json</t>
   </si>
   <si>
-    <t>veridict.fun</t>
+    <t>deflation.site</t>
+  </si>
+  <si>
+    <t>#4d613c</t>
+  </si>
+  <si>
+    <t>oblivioncall.com</t>
+  </si>
+  <si>
+    <t>#a9b4c4</t>
+  </si>
+  <si>
+    <t>elogy.fun</t>
+  </si>
+  <si>
+    <t>#c4b091</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t> read.vorthen.cloud</t>
+  </si>
+  <si>
+    <t>#e9eeb9</t>
+  </si>
+  <si>
+    <t>#ed9874</t>
+  </si>
+  <si>
+    <t> sec.vorthen.cloud</t>
+  </si>
+  <si>
+    <t>#e4c6d0</t>
+  </si>
+  <si>
+    <t>#425066</t>
+  </si>
+  <si>
+    <t>play.kaleidos.fun</t>
+  </si>
+  <si>
+    <t>#f53d93</t>
+  </si>
+  <si>
+    <t>sec.kaleidos.fun</t>
+  </si>
+  <si>
+    <t>#ff978a</t>
+  </si>
+  <si>
+    <t>play.fervid.site</t>
+  </si>
+  <si>
+    <t>#6ae966</t>
+  </si>
+  <si>
+    <t>sec.fervid.site</t>
   </si>
   <si>
     <t>#a515f9</t>
   </si>
   <si>
-    <t>xeromancer.cloud</t>
-  </si>
-  <si>
-    <t>#00000e</t>
-  </si>
-  <si>
-    <t>balefire.cloud</t>
-  </si>
-  <si>
-    <t>#73AE52</t>
-  </si>
-  <si>
-    <t>puttable.site</t>
-  </si>
-  <si>
-    <t>#ffb400</t>
-  </si>
-  <si>
-    <t>color</t>
-  </si>
-  <si>
-    <t>hfwinfo.top</t>
-  </si>
-  <si>
-    <t>#664b3a</t>
-  </si>
-  <si>
-    <t>jkif.top</t>
-  </si>
-  <si>
-    <t>#e07563</t>
-  </si>
-  <si>
-    <t>mcif.top</t>
-  </si>
-  <si>
-    <t>#41bbcb</t>
-  </si>
-  <si>
-    <t>haberdasher.cloud</t>
-  </si>
-  <si>
-    <t>#fb9966</t>
-  </si>
-  <si>
-    <t>melancholy.cloud</t>
-  </si>
-  <si>
-    <t>#afcd53</t>
-  </si>
-  <si>
-    <t>insulary.fun</t>
-  </si>
-  <si>
-    <t>#ed6d46</t>
-  </si>
-  <si>
-    <t>vapourous.fun</t>
-  </si>
-  <si>
-    <t>#7d929f</t>
-  </si>
-  <si>
-    <t>unsdgaction.com</t>
-  </si>
-  <si>
-    <t>#ddbb99</t>
+    <t>日期</t>
   </si>
   <si>
     <t>周一</t>
@@ -153,7 +144,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -170,6 +161,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF2972F4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -178,7 +184,44 @@
     </font>
     <font>
       <sz val="10.5"/>
+      <color rgb="FFFBF1D7"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF2972F4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -193,66 +236,6 @@
     </font>
     <font>
       <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF2972F4"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF2972F4"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFCE9178"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFFBF1D7"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
@@ -403,49 +386,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFB9966"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFCD53"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED6D46"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7D929F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDBB99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF664B3A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE07563"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41BBCB"/>
+        <fgColor rgb="FFF53D93"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE63946"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF978A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AE966"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -457,19 +416,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00000E"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73AE52"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFB400"/>
+        <fgColor rgb="FFE9EEB9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9874"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4C6D0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF425066"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4D613C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9B4C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4B091"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -784,165 +767,169 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -950,62 +937,50 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1395,6 +1370,324 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A6" r:id="rId1" tooltip="https://unsdgaction.com"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="27.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="17"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="D21" s="19"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F16" r:id="rId1"/>
+    <hyperlink ref="F17" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
@@ -1419,419 +1712,94 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3">
+      <c r="A2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7">
+        <v>16</v>
+      </c>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7">
         <v>2</v>
       </c>
-      <c r="E2" s="3">
-        <v>13</v>
-      </c>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3">
+      <c r="E3" s="7">
+        <v>16</v>
+      </c>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="7">
         <v>3</v>
       </c>
-      <c r="E3" s="3">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="3">
+      <c r="E4" s="7">
+        <v>16</v>
+      </c>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="7">
         <v>4</v>
       </c>
-      <c r="E4" s="3">
-        <v>13</v>
-      </c>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="3">
-        <v>5</v>
-      </c>
-      <c r="E5" s="3">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3"/>
+      <c r="E5" s="7">
+        <v>16</v>
+      </c>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="3"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="3"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="7"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A7" r:id="rId1" tooltip="http://game.cheiloproclitic.com"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
-  <cols>
-    <col min="1" max="1" width="27.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="12"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="12"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="16"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F16" r:id="rId1"/>
-    <hyperlink ref="F17" r:id="rId2"/>
-    <hyperlink ref="A2" r:id="rId3" display="hfwinfo.top" tooltip="http://hfwinfo.top"/>
-    <hyperlink ref="A3" r:id="rId4" display="jkif.top" tooltip="http://jkif.top"/>
-    <hyperlink ref="A4" r:id="rId5" display="mcif.top" tooltip="http://mcif.top"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
-  <cols>
-    <col min="1" max="1" width="15.375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A6" r:id="rId1" display="unsdgaction.com" tooltip="https://unsdgaction.com"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1840,34 +1808,37 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="7"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="D2" s="2"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="E2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
